--- a/Ivent_CANTINEmars2026 - Copy.xlsx
+++ b/Ivent_CANTINEmars2026 - Copy.xlsx
@@ -1606,6 +1606,10 @@
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="18.21875" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
